--- a/Main/Tasks/Task3/B747_FC5.xlsx
+++ b/Main/Tasks/Task3/B747_FC5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AE\4th Year\Second Term\Design of control systems for Aeronautical and Space vehicles_AER4420\Autopilot_Team3\Autopilot_Team3\Main\Tasks\Task3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB324BC3-CD27-45D4-9510-978E890CC19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E5707D-77D8-4B30-93F9-A0C56EF302F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -647,16 +647,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -666,10 +657,19 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1248,17 +1248,17 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1">
@@ -1275,7 +1275,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1">
@@ -1292,7 +1292,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1">
@@ -1309,7 +1309,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="13" t="s">
         <v>125</v>
       </c>
       <c r="B5" s="1">
@@ -1327,7 +1327,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="13" t="s">
         <v>126</v>
       </c>
       <c r="B6" s="1">
@@ -1345,7 +1345,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="13" t="s">
         <v>127</v>
       </c>
       <c r="B7" s="1">
@@ -1363,7 +1363,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="13" t="s">
         <v>87</v>
       </c>
       <c r="B8" s="1">
@@ -1373,7 +1373,7 @@
       <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="13" t="s">
         <v>88</v>
       </c>
       <c r="B9" s="1">
@@ -1382,7 +1382,7 @@
       <c r="C9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="23" t="s">
         <v>137</v>
       </c>
       <c r="E9" s="5">
@@ -1390,7 +1390,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B10" s="1">
@@ -1399,13 +1399,13 @@
       <c r="C10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="12"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="5">
         <v>33100000</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="13" t="s">
         <v>84</v>
       </c>
       <c r="B11" s="1">
@@ -1414,13 +1414,13 @@
       <c r="C11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="12"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="5">
         <v>49700000</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="13" t="s">
         <v>85</v>
       </c>
       <c r="B12" s="3">
@@ -1430,13 +1430,13 @@
       <c r="C12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="12"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="5">
         <v>970056</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B13" s="1">
@@ -1454,7 +1454,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="13" t="s">
         <v>128</v>
       </c>
       <c r="B14" s="1">
@@ -1472,7 +1472,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="13" t="s">
         <v>129</v>
       </c>
       <c r="B15" s="1">
@@ -1491,7 +1491,7 @@
       <c r="I15" s="10"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="13" t="s">
         <v>130</v>
       </c>
       <c r="B16" s="3">
@@ -1509,7 +1509,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="14" t="s">
         <v>124</v>
       </c>
       <c r="B17" s="3">
@@ -1527,7 +1527,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="14" t="s">
         <v>5</v>
       </c>
       <c r="B18" s="3">
@@ -1538,15 +1538,15 @@
       <c r="E18" s="5">
         <v>86</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K18" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
     </row>
     <row r="19" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="14" t="s">
         <v>83</v>
       </c>
       <c r="B19" s="3">
@@ -1557,13 +1557,13 @@
       <c r="E19" s="5">
         <v>-10</v>
       </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
     </row>
     <row r="20" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="14" t="s">
         <v>81</v>
       </c>
       <c r="B20" s="3">
@@ -1579,13 +1579,13 @@
       <c r="E20" s="5">
         <v>2.5</v>
       </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
     </row>
     <row r="21" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="14" t="s">
         <v>82</v>
       </c>
       <c r="B21" s="1">
@@ -1601,13 +1601,13 @@
       <c r="E21" s="5">
         <v>2.5</v>
       </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="15" t="s">
         <v>90</v>
       </c>
       <c r="B22" s="2">
@@ -1623,31 +1623,31 @@
       <c r="E22" s="5">
         <v>10</v>
       </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="15" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="2">
         <f t="shared" si="0"/>
         <v>-6.7900000000000002E-2</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B24" s="2">
@@ -1663,13 +1663,13 @@
       <c r="E24" s="5">
         <v>20000</v>
       </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B25" s="2">
@@ -1687,7 +1687,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="15" t="s">
         <v>93</v>
       </c>
       <c r="B26" s="2">
@@ -1705,7 +1705,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="15" t="s">
         <v>97</v>
       </c>
       <c r="B27" s="2">
@@ -1723,7 +1723,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="15" t="s">
         <v>98</v>
       </c>
       <c r="B28" s="2">
@@ -1741,7 +1741,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="15" t="s">
         <v>94</v>
       </c>
       <c r="B29" s="2">
@@ -1759,7 +1759,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="15" t="s">
         <v>99</v>
       </c>
       <c r="B30" s="2">
@@ -1777,7 +1777,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="15" t="s">
         <v>95</v>
       </c>
       <c r="B31" s="2">
@@ -1795,7 +1795,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="15" t="s">
         <v>100</v>
       </c>
       <c r="B32" s="2">
@@ -1813,7 +1813,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="15" t="s">
         <v>101</v>
       </c>
       <c r="B33" s="2">
@@ -1831,7 +1831,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="15" t="s">
         <v>102</v>
       </c>
       <c r="B34" s="2">
@@ -1849,7 +1849,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="15" t="s">
         <v>41</v>
       </c>
       <c r="B35" s="2">
@@ -1867,7 +1867,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="15" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="2">
@@ -1885,7 +1885,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="15" t="s">
         <v>43</v>
       </c>
       <c r="B37" s="2">
@@ -1903,7 +1903,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="16" t="s">
         <v>103</v>
       </c>
       <c r="B38" s="3">
@@ -1921,7 +1921,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="16" t="s">
         <v>104</v>
       </c>
       <c r="B39" s="3">
@@ -1936,7 +1936,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
+      <c r="A40" s="16" t="s">
         <v>105</v>
       </c>
       <c r="B40" s="3">
@@ -1951,7 +1951,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="19" t="s">
+      <c r="A41" s="16" t="s">
         <v>106</v>
       </c>
       <c r="B41" s="3">
@@ -1966,21 +1966,21 @@
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="16" t="s">
         <v>107</v>
       </c>
       <c r="B42" s="3">
         <f t="shared" si="1"/>
         <v>-0.65200000000000002</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="19" t="s">
+      <c r="A43" s="16" t="s">
         <v>108</v>
       </c>
       <c r="B43" s="3">
@@ -1998,7 +1998,7 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="16" t="s">
         <v>109</v>
       </c>
       <c r="B44" s="3">
@@ -2016,7 +2016,7 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="19" t="s">
+      <c r="A45" s="16" t="s">
         <v>110</v>
       </c>
       <c r="B45" s="3">
@@ -2034,7 +2034,7 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="19" t="s">
+      <c r="A46" s="16" t="s">
         <v>111</v>
       </c>
       <c r="B46" s="3">
@@ -2052,7 +2052,7 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="16" t="s">
         <v>112</v>
       </c>
       <c r="B47" s="2">
@@ -2070,7 +2070,7 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="16" t="s">
         <v>113</v>
       </c>
       <c r="B48" s="3">
@@ -2088,7 +2088,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
+      <c r="A49" s="16" t="s">
         <v>114</v>
       </c>
       <c r="B49" s="3">
@@ -2106,7 +2106,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="19" t="s">
+      <c r="A50" s="16" t="s">
         <v>115</v>
       </c>
       <c r="B50" s="3">
@@ -2124,7 +2124,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
+      <c r="A51" s="16" t="s">
         <v>116</v>
       </c>
       <c r="B51" s="3">
@@ -2142,7 +2142,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="20" t="s">
+      <c r="A52" s="17" t="s">
         <v>117</v>
       </c>
       <c r="B52" s="1">
@@ -2160,7 +2160,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="20" t="s">
+      <c r="A53" s="17" t="s">
         <v>118</v>
       </c>
       <c r="B53" s="1">
@@ -2177,7 +2177,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="20" t="s">
+      <c r="A54" s="17" t="s">
         <v>119</v>
       </c>
       <c r="B54" s="3">
@@ -2195,7 +2195,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="20" t="s">
+      <c r="A55" s="17" t="s">
         <v>120</v>
       </c>
       <c r="B55" s="3">
@@ -2213,7 +2213,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="20" t="s">
+      <c r="A56" s="17" t="s">
         <v>121</v>
       </c>
       <c r="B56" s="3">
@@ -2231,7 +2231,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="20" t="s">
+      <c r="A57" s="17" t="s">
         <v>122</v>
       </c>
       <c r="B57" s="3">
@@ -2249,11 +2249,11 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="18" t="s">
         <v>133</v>
       </c>
       <c r="B58" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>58</v>
@@ -2266,7 +2266,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="21" t="s">
+      <c r="A59" s="18" t="s">
         <v>134</v>
       </c>
       <c r="B59" s="1">
@@ -2274,77 +2274,77 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="21" t="s">
+      <c r="A60" s="18" t="s">
         <v>135</v>
       </c>
       <c r="B60" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="21" t="s">
+      <c r="A61" s="18" t="s">
         <v>123</v>
       </c>
       <c r="B61" s="1">
         <v>0</v>
       </c>
-      <c r="C61" s="22" t="s">
+      <c r="C61" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="1"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="1"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
     </row>
     <row r="64" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="1"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="1"/>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="D65" s="23"/>
-      <c r="E65" s="23"/>
-      <c r="F65" s="23"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="1"/>
-      <c r="C66" s="23"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="23"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="1"/>
-      <c r="C67" s="23"/>
-      <c r="D67" s="23"/>
-      <c r="E67" s="23"/>
-      <c r="F67" s="23"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="1"/>
-      <c r="C68" s="23"/>
-      <c r="D68" s="23"/>
-      <c r="E68" s="23"/>
-      <c r="F68" s="23"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B69" s="1"/>

--- a/Main/Tasks/Task3/B747_FC5.xlsx
+++ b/Main/Tasks/Task3/B747_FC5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AE\4th Year\Second Term\Design of control systems for Aeronautical and Space vehicles_AER4420\Autopilot_Team3\Autopilot_Team3\Main\Tasks\Task3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0984A5D5-0401-4232-A462-EDB18DB02620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59EB1522-DC32-47D4-9C63-9DDA4FE1E250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="0" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2286,7 +2286,7 @@
         <v>123</v>
       </c>
       <c r="B61" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C61" s="21" t="s">
         <v>132</v>
